--- a/artfynd/A 29679-2023 artfynd.xlsx
+++ b/artfynd/A 29679-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29679-2023 artfynd.xlsx
+++ b/artfynd/A 29679-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69565195</v>
+        <v>69506452</v>
       </c>
       <c r="B2" t="n">
-        <v>88488</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>889</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hargs tallpark, intill NR, Upl</t>
+          <t>Hargs tallparks NR, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687769.8793066399</v>
+        <v>687744</v>
       </c>
       <c r="R2" t="n">
-        <v>6677520.656224729</v>
+        <v>6677544</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-03-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-09-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-09-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På döende gren 16 m upp, på levande tall, omkr. 190 cm, minst 250 år.</t>
+          <t>2 ex. i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gammal, grov tallskog.</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Döende gren på gammal, levande tall. # Tall</t>
+          <t>Gammal barrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,6 +788,495 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69565195</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90946</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>889</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hargs tallpark, intill NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>687770</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6677521</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2002-03-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2002-03-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På döende gren 16 m upp, på levande tall, omkr. 190 cm, minst 250 år.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gammal, grov tallskog.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Döende gren på gammal, levande tall. # Tall</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>56165909</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92692</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hargs tallpark, intill NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>687919</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6677581</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2005-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2005-09-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5 ex. i kanten av en grusväg, i en 50-årig tallplantering. Hatt upp till 7 cm bred, vitgul med fjälligt uppsprucken, ljusbrun mitt. Fot med tydliga orange fläckar vid basen. Sporer amyloida.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>50-årig tallplantering.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>85399847</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hargs tallparks NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>687756</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6677418</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2001-03-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2001-03-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kådflöde, gnagmjöl och kläckhål i levande tall, omkr. 255 cm, i ganska solexponerat läge.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110570835</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alvsjön, SO-sidan, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>687784</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6677669</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enorma mängder små paddor på skogsbilvägen och i kärret vid Alvsjöns SO-ände.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Sjöstrand med viden och klibbal samt angränsande skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29679-2023 artfynd.xlsx
+++ b/artfynd/A 29679-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506452</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69565195</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56165909</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85399847</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,8 +1302,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110570835</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>